--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/2_fold/129.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/2_fold/129.xlsx
@@ -426,13 +426,13 @@
         <v>-4.391681991724199</v>
       </c>
       <c r="E2">
-        <v>-20.78317884276387</v>
+        <v>-16.65355360504903</v>
       </c>
       <c r="F2">
-        <v>-2.126337261860962</v>
+        <v>-3.937706724010168</v>
       </c>
       <c r="G2">
-        <v>-11.59656011994108</v>
+        <v>-12.03803833567063</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-4.757668327661049</v>
       </c>
       <c r="E3">
-        <v>-20.85306077651544</v>
+        <v>-17.05450047313666</v>
       </c>
       <c r="F3">
-        <v>-1.744774668783453</v>
+        <v>-3.648901399228537</v>
       </c>
       <c r="G3">
-        <v>-11.89600077619112</v>
+        <v>-12.33574154139528</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-5.213235336139137</v>
       </c>
       <c r="E4">
-        <v>-20.14306514732467</v>
+        <v>-17.02880870788126</v>
       </c>
       <c r="F4">
-        <v>-1.319693794199873</v>
+        <v>-3.173951978629023</v>
       </c>
       <c r="G4">
-        <v>-11.83500333956435</v>
+        <v>-12.65031146255082</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-5.700650662370187</v>
       </c>
       <c r="E5">
-        <v>-20.23019952091958</v>
+        <v>-18.47319177637351</v>
       </c>
       <c r="F5">
-        <v>-1.331823578079066</v>
+        <v>-3.211273243594752</v>
       </c>
       <c r="G5">
-        <v>-12.82029182138902</v>
+        <v>-12.69705945519929</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-6.205798030731321</v>
       </c>
       <c r="E6">
-        <v>-23.04015847301545</v>
+        <v>-17.99790242557146</v>
       </c>
       <c r="F6">
-        <v>-1.706125530871037</v>
+        <v>-2.752546570211665</v>
       </c>
       <c r="G6">
-        <v>-11.6301917317638</v>
+        <v>-13.43445121123628</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-6.696110154755226</v>
       </c>
       <c r="E7">
-        <v>-22.66459603254518</v>
+        <v>-19.87814840975916</v>
       </c>
       <c r="F7">
-        <v>-1.87683300013775</v>
+        <v>-2.904682042307613</v>
       </c>
       <c r="G7">
-        <v>-12.29863763926638</v>
+        <v>-13.97235205694942</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-7.146629748240254</v>
       </c>
       <c r="E8">
-        <v>-25.24622388563595</v>
+        <v>-19.95421032196207</v>
       </c>
       <c r="F8">
-        <v>-1.814489241035657</v>
+        <v>-2.633009840518085</v>
       </c>
       <c r="G8">
-        <v>-13.17602013102346</v>
+        <v>-13.29843925027305</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-7.525668307996902</v>
       </c>
       <c r="E9">
-        <v>-22.96524284713819</v>
+        <v>-21.61671589602299</v>
       </c>
       <c r="F9">
-        <v>-1.542973600685257</v>
+        <v>-2.021609256227229</v>
       </c>
       <c r="G9">
-        <v>-11.86349831140405</v>
+        <v>-13.63732303580563</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-7.808151451334308</v>
       </c>
       <c r="E10">
-        <v>-23.89157925423927</v>
+        <v>-22.01009145986545</v>
       </c>
       <c r="F10">
-        <v>-1.398492243391176</v>
+        <v>-1.644828828166082</v>
       </c>
       <c r="G10">
-        <v>-11.80797821692943</v>
+        <v>-14.39015212460987</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-7.97184943902869</v>
       </c>
       <c r="E11">
-        <v>-24.60107234485973</v>
+        <v>-21.85003084861788</v>
       </c>
       <c r="F11">
-        <v>-1.155033406973596</v>
+        <v>-1.965609963063176</v>
       </c>
       <c r="G11">
-        <v>-11.65923365459535</v>
+        <v>-13.02668162429489</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-8.000081317632873</v>
       </c>
       <c r="E12">
-        <v>-28.15834560650562</v>
+        <v>-22.91706559577018</v>
       </c>
       <c r="F12">
-        <v>-0.8534579703104076</v>
+        <v>-1.310095501103635</v>
       </c>
       <c r="G12">
-        <v>-11.03558551353168</v>
+        <v>-12.30387609828845</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-7.882908065397599</v>
       </c>
       <c r="E13">
-        <v>-26.51435297192512</v>
+        <v>-24.13987899329415</v>
       </c>
       <c r="F13">
-        <v>-0.4676152028626342</v>
+        <v>-1.132089286650855</v>
       </c>
       <c r="G13">
-        <v>-11.40439104282301</v>
+        <v>-11.77613757589622</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-7.624101651637706</v>
       </c>
       <c r="E14">
-        <v>-27.85622232528662</v>
+        <v>-24.78324465320069</v>
       </c>
       <c r="F14">
-        <v>-0.2710659840981872</v>
+        <v>-0.981516115476586</v>
       </c>
       <c r="G14">
-        <v>-10.2180765328549</v>
+        <v>-12.44126392165119</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-7.233996325063453</v>
       </c>
       <c r="E15">
-        <v>-27.9154180462994</v>
+        <v>-25.28657648686798</v>
       </c>
       <c r="F15">
-        <v>0.8047314484479196</v>
+        <v>-0.8198892096793604</v>
       </c>
       <c r="G15">
-        <v>-10.37752775875715</v>
+        <v>-11.88137669036399</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-6.732361015864316</v>
       </c>
       <c r="E16">
-        <v>-28.57258482743835</v>
+        <v>-27.8379523486687</v>
       </c>
       <c r="F16">
-        <v>0.2681705455303874</v>
+        <v>-0.8690205087068019</v>
       </c>
       <c r="G16">
-        <v>-9.055458446168037</v>
+        <v>-10.147891886012</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-6.153989368355064</v>
       </c>
       <c r="E17">
-        <v>-29.96438408734694</v>
+        <v>-27.86928417490321</v>
       </c>
       <c r="F17">
-        <v>0.07015263136077678</v>
+        <v>-0.04244486459955162</v>
       </c>
       <c r="G17">
-        <v>-9.228951561853584</v>
+        <v>-9.861058515392456</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-5.534992280881811</v>
       </c>
       <c r="E18">
-        <v>-30.82610690926201</v>
+        <v>-28.50501623239472</v>
       </c>
       <c r="F18">
-        <v>1.57971719907622</v>
+        <v>-0.1944511113806637</v>
       </c>
       <c r="G18">
-        <v>-7.656722007916297</v>
+        <v>-9.353454055286891</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-4.912729716889999</v>
       </c>
       <c r="E19">
-        <v>-32.09806940960399</v>
+        <v>-28.76673499724011</v>
       </c>
       <c r="F19">
-        <v>1.524599288828746</v>
+        <v>0.2557541465298256</v>
       </c>
       <c r="G19">
-        <v>-7.516859198681177</v>
+        <v>-9.396014413611219</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-4.330166407044048</v>
       </c>
       <c r="E20">
-        <v>-32.04687900341982</v>
+        <v>-30.68435988335127</v>
       </c>
       <c r="F20">
-        <v>0.7039622106321654</v>
+        <v>0.4920865381811217</v>
       </c>
       <c r="G20">
-        <v>-8.414468434157904</v>
+        <v>-7.420802072940345</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-3.818047611314453</v>
       </c>
       <c r="E21">
-        <v>-33.440181725828</v>
+        <v>-32.69891241536128</v>
       </c>
       <c r="F21">
-        <v>1.476630189267432</v>
+        <v>0.7248039344866009</v>
       </c>
       <c r="G21">
-        <v>-6.901582410148917</v>
+        <v>-7.883283728905404</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-3.398054966041399</v>
       </c>
       <c r="E22">
-        <v>-34.20559157712029</v>
+        <v>-32.27552574648561</v>
       </c>
       <c r="F22">
-        <v>0.8963985852417129</v>
+        <v>0.8169830023353243</v>
       </c>
       <c r="G22">
-        <v>-7.195001383999548</v>
+        <v>-7.249743476586012</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-3.090133018863716</v>
       </c>
       <c r="E23">
-        <v>-35.67618140907221</v>
+        <v>-33.82489784405819</v>
       </c>
       <c r="F23">
-        <v>1.374108126027354</v>
+        <v>1.133141018757395</v>
       </c>
       <c r="G23">
-        <v>-7.664669114451646</v>
+        <v>-7.199450092782805</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-2.898840237280079</v>
       </c>
       <c r="E24">
-        <v>-34.46973166416806</v>
+        <v>-33.96327661558449</v>
       </c>
       <c r="F24">
-        <v>1.977007175663279</v>
+        <v>1.593842520028757</v>
       </c>
       <c r="G24">
-        <v>-8.21861168030488</v>
+        <v>-7.16135149696469</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-2.821624336367561</v>
       </c>
       <c r="E25">
-        <v>-34.22450945470489</v>
+        <v>-34.5973619247857</v>
       </c>
       <c r="F25">
-        <v>2.357885537266075</v>
+        <v>1.939097769841563</v>
       </c>
       <c r="G25">
-        <v>-7.563750782282162</v>
+        <v>-6.781292353113373</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-2.855099014025154</v>
       </c>
       <c r="E26">
-        <v>-35.45833093884531</v>
+        <v>-34.20009480193188</v>
       </c>
       <c r="F26">
-        <v>1.958483223801877</v>
+        <v>1.76766879256701</v>
       </c>
       <c r="G26">
-        <v>-7.144128414897115</v>
+        <v>-7.116963617426581</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-2.983424109078158</v>
       </c>
       <c r="E27">
-        <v>-35.72191864878688</v>
+        <v>-35.88615531402156</v>
       </c>
       <c r="F27">
-        <v>2.38588766895031</v>
+        <v>1.445607830032591</v>
       </c>
       <c r="G27">
-        <v>-7.956955025149735</v>
+        <v>-6.818064690679203</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-3.188785949680485</v>
       </c>
       <c r="E28">
-        <v>-37.08452290968759</v>
+        <v>-36.53152489839233</v>
       </c>
       <c r="F28">
-        <v>2.520159398004887</v>
+        <v>1.721591684153691</v>
       </c>
       <c r="G28">
-        <v>-5.895688626638879</v>
+        <v>-6.707935651592272</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-3.453747023233552</v>
       </c>
       <c r="E29">
-        <v>-36.09047462175216</v>
+        <v>-35.89638882672594</v>
       </c>
       <c r="F29">
-        <v>2.144249584084083</v>
+        <v>1.793712663711027</v>
       </c>
       <c r="G29">
-        <v>-6.610445227070919</v>
+        <v>-6.72737264507311</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-3.75381965188387</v>
       </c>
       <c r="E30">
-        <v>-36.76042291074327</v>
+        <v>-36.71300362044204</v>
       </c>
       <c r="F30">
-        <v>2.654222378473959</v>
+        <v>1.539917458841314</v>
       </c>
       <c r="G30">
-        <v>-6.852051363766316</v>
+        <v>-6.572806122300839</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-4.0669675373419</v>
       </c>
       <c r="E31">
-        <v>-37.54132839348849</v>
+        <v>-36.26826736875108</v>
       </c>
       <c r="F31">
-        <v>1.922803783028496</v>
+        <v>1.223747845275605</v>
       </c>
       <c r="G31">
-        <v>-5.865560634057432</v>
+        <v>-7.168337849490508</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-4.373491390556072</v>
       </c>
       <c r="E32">
-        <v>-36.81339089137447</v>
+        <v>-35.98690183773359</v>
       </c>
       <c r="F32">
-        <v>2.089323855074058</v>
+        <v>1.410596053385867</v>
       </c>
       <c r="G32">
-        <v>-8.036893413785032</v>
+        <v>-6.702481806141436</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-4.651624800077226</v>
       </c>
       <c r="E33">
-        <v>-37.29444074628406</v>
+        <v>-35.20159810419537</v>
       </c>
       <c r="F33">
-        <v>1.428750553385621</v>
+        <v>1.100864511274715</v>
       </c>
       <c r="G33">
-        <v>-7.392676521460282</v>
+        <v>-6.77849624565629</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-4.885625356795753</v>
       </c>
       <c r="E34">
-        <v>-35.78485848980899</v>
+        <v>-35.01946317475634</v>
       </c>
       <c r="F34">
-        <v>1.376389449854664</v>
+        <v>1.038034500507178</v>
       </c>
       <c r="G34">
-        <v>-6.468454660994041</v>
+        <v>-6.224963566703861</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-5.063714437907652</v>
       </c>
       <c r="E35">
-        <v>-34.80552295299177</v>
+        <v>-35.55244063086026</v>
       </c>
       <c r="F35">
-        <v>1.597518814562381</v>
+        <v>0.8397465385642546</v>
       </c>
       <c r="G35">
-        <v>-5.883036958350345</v>
+        <v>-6.248246186967409</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-5.17500282684935</v>
       </c>
       <c r="E36">
-        <v>-36.23730310171882</v>
+        <v>-34.65518085624431</v>
       </c>
       <c r="F36">
-        <v>1.157150419560136</v>
+        <v>1.032780994438623</v>
       </c>
       <c r="G36">
-        <v>-6.326884424796332</v>
+        <v>-5.695627268621869</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-5.215590725076104</v>
       </c>
       <c r="E37">
-        <v>-36.22883678043316</v>
+        <v>-35.20564956184274</v>
       </c>
       <c r="F37">
-        <v>0.301378137973814</v>
+        <v>0.6233372113176894</v>
       </c>
       <c r="G37">
-        <v>-5.783523206770879</v>
+        <v>-5.728055327188087</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-5.185992159486848</v>
       </c>
       <c r="E38">
-        <v>-35.19886321453797</v>
+        <v>-33.91867735577282</v>
       </c>
       <c r="F38">
-        <v>0.8637277748753004</v>
+        <v>0.1327531843577382</v>
       </c>
       <c r="G38">
-        <v>-5.085138585669711</v>
+        <v>-5.625270312635957</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-5.088019528488508</v>
       </c>
       <c r="E39">
-        <v>-33.45745493172796</v>
+        <v>-32.99421820019056</v>
       </c>
       <c r="F39">
-        <v>1.349202431694784</v>
+        <v>0.06997453236917489</v>
       </c>
       <c r="G39">
-        <v>-5.315442809030178</v>
+        <v>-5.000670555168831</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-4.927030472443668</v>
       </c>
       <c r="E40">
-        <v>-32.27986585232005</v>
+        <v>-32.74523110466143</v>
       </c>
       <c r="F40">
-        <v>1.184807950404805</v>
+        <v>0.1977709134360686</v>
       </c>
       <c r="G40">
-        <v>-4.411529930738208</v>
+        <v>-4.214564915806257</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-4.711007503651379</v>
       </c>
       <c r="E41">
-        <v>-33.24276505531926</v>
+        <v>-31.95242667147057</v>
       </c>
       <c r="F41">
-        <v>0.4741474137060956</v>
+        <v>-0.1763902168974261</v>
       </c>
       <c r="G41">
-        <v>-4.972158613489284</v>
+        <v>-4.317261165042289</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-4.448004411268382</v>
       </c>
       <c r="E42">
-        <v>-32.66616642067066</v>
+        <v>-32.66846522313896</v>
       </c>
       <c r="F42">
-        <v>-0.01388275655102467</v>
+        <v>-0.0352712028913079</v>
       </c>
       <c r="G42">
-        <v>-5.318875938167492</v>
+        <v>-4.517118884981193</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-4.145742800131833</v>
       </c>
       <c r="E43">
-        <v>-31.58964781545812</v>
+        <v>-32.31274059656173</v>
       </c>
       <c r="F43">
-        <v>-0.2642211842488549</v>
+        <v>-0.5034147569094205</v>
       </c>
       <c r="G43">
-        <v>-5.478677003844945</v>
+        <v>-4.485552372130043</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-3.813887163253836</v>
       </c>
       <c r="E44">
-        <v>-32.59252583067013</v>
+        <v>-31.23234704518312</v>
       </c>
       <c r="F44">
-        <v>0.3855916248772173</v>
+        <v>-0.2477474417093811</v>
       </c>
       <c r="G44">
-        <v>-3.749505149557474</v>
+        <v>-3.924994179482927</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-3.462941507796677</v>
       </c>
       <c r="E45">
-        <v>-32.73422924786195</v>
+        <v>-31.60218636044778</v>
       </c>
       <c r="F45">
-        <v>0.1635104660236839</v>
+        <v>-0.4629788305091654</v>
       </c>
       <c r="G45">
-        <v>-3.633261746638155</v>
+        <v>-3.938956441556201</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-3.101232183150063</v>
       </c>
       <c r="E46">
-        <v>-30.74456483471598</v>
+        <v>-30.03805582643241</v>
       </c>
       <c r="F46">
-        <v>0.4130611163214517</v>
+        <v>-0.642313746276036</v>
       </c>
       <c r="G46">
-        <v>-3.726997920437487</v>
+        <v>-3.989745866831719</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-2.738898837541496</v>
       </c>
       <c r="E47">
-        <v>-29.19935425489087</v>
+        <v>-29.86349012463288</v>
       </c>
       <c r="F47">
-        <v>1.031617966605093</v>
+        <v>-0.5065459856920026</v>
       </c>
       <c r="G47">
-        <v>-3.862735753218648</v>
+        <v>-3.570045177108938</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-2.387875542575851</v>
       </c>
       <c r="E48">
-        <v>-30.94869101811998</v>
+        <v>-30.65029316745936</v>
       </c>
       <c r="F48">
-        <v>0.02544978446870146</v>
+        <v>-0.9181252999773538</v>
       </c>
       <c r="G48">
-        <v>-3.771894895170862</v>
+        <v>-3.182234732566606</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-2.057307192763166</v>
       </c>
       <c r="E49">
-        <v>-31.04877718123136</v>
+        <v>-29.44287572431654</v>
       </c>
       <c r="F49">
-        <v>0.005367673522633044</v>
+        <v>-1.000652230848657</v>
       </c>
       <c r="G49">
-        <v>-4.261354680368189</v>
+        <v>-3.636269324407118</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-1.758005144370718</v>
       </c>
       <c r="E50">
-        <v>-29.12103922554425</v>
+        <v>-29.07583982669614</v>
       </c>
       <c r="F50">
-        <v>0.2011705332571578</v>
+        <v>-1.408878313887476</v>
       </c>
       <c r="G50">
-        <v>-4.341648130267878</v>
+        <v>-2.96989765348218</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-1.502424487451174</v>
       </c>
       <c r="E51">
-        <v>-27.97543194994318</v>
+        <v>-28.41756829134479</v>
       </c>
       <c r="F51">
-        <v>0.1687722557662663</v>
+        <v>-0.6267006774680709</v>
       </c>
       <c r="G51">
-        <v>-3.90075341595444</v>
+        <v>-3.238185599898755</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-1.300079882430469</v>
       </c>
       <c r="E52">
-        <v>-28.55809842633735</v>
+        <v>-27.76730207082204</v>
       </c>
       <c r="F52">
-        <v>0.02592775246011677</v>
+        <v>-1.076923331094019</v>
       </c>
       <c r="G52">
-        <v>-3.798401785004435</v>
+        <v>-3.053329218380387</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-1.159837078205851</v>
       </c>
       <c r="E53">
-        <v>-28.43795432913271</v>
+        <v>-27.27590656650231</v>
       </c>
       <c r="F53">
-        <v>0.5306917726211899</v>
+        <v>-1.411565537742158</v>
       </c>
       <c r="G53">
-        <v>-3.276406900712653</v>
+        <v>-3.551649870719954</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-1.087219917817107</v>
       </c>
       <c r="E54">
-        <v>-27.58977305274225</v>
+        <v>-26.85664403647219</v>
       </c>
       <c r="F54">
-        <v>-0.30855706438149</v>
+        <v>-1.415130831043807</v>
       </c>
       <c r="G54">
-        <v>-3.948892935469978</v>
+        <v>-2.958979519602144</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-1.079015471181055</v>
       </c>
       <c r="E55">
-        <v>-24.40921474770928</v>
+        <v>-26.16562027661324</v>
       </c>
       <c r="F55">
-        <v>-1.00817463523348</v>
+        <v>-1.450220474226394</v>
       </c>
       <c r="G55">
-        <v>-4.787456265901792</v>
+        <v>-3.944645254020236</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-1.126527321212209</v>
       </c>
       <c r="E56">
-        <v>-25.96213368775327</v>
+        <v>-24.72152377970241</v>
       </c>
       <c r="F56">
-        <v>-0.615838295715161</v>
+        <v>-1.654371620646332</v>
       </c>
       <c r="G56">
-        <v>-3.935729561241585</v>
+        <v>-3.63946487578664</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-1.219237309038794</v>
       </c>
       <c r="E57">
-        <v>-26.12819984257654</v>
+        <v>-26.12358977800598</v>
       </c>
       <c r="F57">
-        <v>-0.4798112561340514</v>
+        <v>-1.645948780894667</v>
       </c>
       <c r="G57">
-        <v>-4.768951308239981</v>
+        <v>-3.182856089779291</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-1.34445090828065</v>
       </c>
       <c r="E58">
-        <v>-26.0764549826805</v>
+        <v>-24.93044276897526</v>
       </c>
       <c r="F58">
-        <v>0.1761024789136391</v>
+        <v>-1.812603048459482</v>
       </c>
       <c r="G58">
-        <v>-4.870551044747746</v>
+        <v>-4.328625736247405</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-1.490501059081859</v>
       </c>
       <c r="E59">
-        <v>-23.76587816028201</v>
+        <v>-23.0793606347105</v>
       </c>
       <c r="F59">
-        <v>-1.196854363671331</v>
+        <v>-1.810869275485423</v>
       </c>
       <c r="G59">
-        <v>-4.651932514177101</v>
+        <v>-4.02417636649932</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-1.647184246705474</v>
       </c>
       <c r="E60">
-        <v>-23.67800036185997</v>
+        <v>-22.413351666661</v>
       </c>
       <c r="F60">
-        <v>-1.131989882562519</v>
+        <v>-1.790095477758017</v>
       </c>
       <c r="G60">
-        <v>-6.992039488741811</v>
+        <v>-4.366489365052321</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-1.803633397953429</v>
       </c>
       <c r="E61">
-        <v>-25.08868427366255</v>
+        <v>-24.16615636134634</v>
       </c>
       <c r="F61">
-        <v>-0.1788703489014078</v>
+        <v>-1.668757048963348</v>
       </c>
       <c r="G61">
-        <v>-5.278495551576743</v>
+        <v>-4.888682665933027</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-1.949982799644414</v>
       </c>
       <c r="E62">
-        <v>-22.35192567116679</v>
+        <v>-22.60405051785183</v>
       </c>
       <c r="F62">
-        <v>-0.8607302077395844</v>
+        <v>-1.678909519852059</v>
       </c>
       <c r="G62">
-        <v>-5.999405677010037</v>
+        <v>-4.837044748665398</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-2.077721634267086</v>
       </c>
       <c r="E63">
-        <v>-23.15654806718244</v>
+        <v>-23.36383069119331</v>
       </c>
       <c r="F63">
-        <v>-0.9651558592712958</v>
+        <v>-2.047456804296782</v>
       </c>
       <c r="G63">
-        <v>-6.892228112278959</v>
+        <v>-4.808149027530956</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-2.178412120424213</v>
       </c>
       <c r="E64">
-        <v>-23.26178213573095</v>
+        <v>-22.49943527779072</v>
       </c>
       <c r="F64">
-        <v>-0.4862236481991223</v>
+        <v>-2.20691587260088</v>
       </c>
       <c r="G64">
-        <v>-7.434276125775081</v>
+        <v>-6.582442380586638</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-2.24465146700566</v>
       </c>
       <c r="E65">
-        <v>-23.02254055057552</v>
+        <v>-22.56879390691536</v>
       </c>
       <c r="F65">
-        <v>-0.5028100487053768</v>
+        <v>-2.15447358906445</v>
       </c>
       <c r="G65">
-        <v>-6.504519486775679</v>
+        <v>-6.053850144713113</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-2.27093506909629</v>
       </c>
       <c r="E66">
-        <v>-20.95088966927177</v>
+        <v>-20.97129439651066</v>
       </c>
       <c r="F66">
-        <v>-1.348275783066067</v>
+        <v>-2.323726445171847</v>
       </c>
       <c r="G66">
-        <v>-5.325491564961373</v>
+        <v>-6.911231722157672</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-2.251966042706343</v>
       </c>
       <c r="E67">
-        <v>-20.19682016150193</v>
+        <v>-21.25956464135568</v>
       </c>
       <c r="F67">
-        <v>-1.957052927792257</v>
+        <v>-2.545960851994899</v>
       </c>
       <c r="G67">
-        <v>-6.844234794460523</v>
+        <v>-6.720574266157851</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-2.182763300198254</v>
       </c>
       <c r="E68">
-        <v>-22.70876543498473</v>
+        <v>-21.4747176008271</v>
       </c>
       <c r="F68">
-        <v>-0.9817066399792298</v>
+        <v>-2.411547472114442</v>
       </c>
       <c r="G68">
-        <v>-8.0246229142068</v>
+        <v>-7.286147699164496</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-2.061803011003803</v>
       </c>
       <c r="E69">
-        <v>-20.61217451967538</v>
+        <v>-21.17646718916851</v>
       </c>
       <c r="F69">
-        <v>-1.637193765814479</v>
+        <v>-2.766310722976581</v>
       </c>
       <c r="G69">
-        <v>-6.922776434739575</v>
+        <v>-7.509478623722099</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-1.888915818771411</v>
       </c>
       <c r="E70">
-        <v>-22.20259280477125</v>
+        <v>-20.85451440047913</v>
       </c>
       <c r="F70">
-        <v>-1.653055344843284</v>
+        <v>-2.359460558193812</v>
       </c>
       <c r="G70">
-        <v>-6.536300080683302</v>
+        <v>-7.864317974823261</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-1.664023375043437</v>
       </c>
       <c r="E71">
-        <v>-21.84822420169158</v>
+        <v>-20.61506100154614</v>
       </c>
       <c r="F71">
-        <v>-1.393889834101222</v>
+        <v>-3.229994346898021</v>
       </c>
       <c r="G71">
-        <v>-6.659226989755871</v>
+        <v>-7.975764134556409</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-1.392130178132858</v>
       </c>
       <c r="E72">
-        <v>-23.77129810106091</v>
+        <v>-22.41655794580377</v>
       </c>
       <c r="F72">
-        <v>-2.156349841231791</v>
+        <v>-3.109610197351377</v>
       </c>
       <c r="G72">
-        <v>-7.399318255700075</v>
+        <v>-8.09637270243207</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-1.079508871997888</v>
       </c>
       <c r="E73">
-        <v>-23.11504502641343</v>
+        <v>-21.57937437300145</v>
       </c>
       <c r="F73">
-        <v>-1.808331157763245</v>
+        <v>-2.924268789546808</v>
       </c>
       <c r="G73">
-        <v>-6.676335199061437</v>
+        <v>-6.957561995671568</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-0.7312550899161085</v>
       </c>
       <c r="E74">
-        <v>-24.94451384894378</v>
+        <v>-21.18759779551905</v>
       </c>
       <c r="F74">
-        <v>-1.85780374416064</v>
+        <v>-3.439358409383777</v>
       </c>
       <c r="G74">
-        <v>-6.15245274643028</v>
+        <v>-7.195176303887153</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-0.3581702217865529</v>
       </c>
       <c r="E75">
-        <v>-22.06455667317925</v>
+        <v>-21.29115396669233</v>
       </c>
       <c r="F75">
-        <v>-2.27671493832817</v>
+        <v>-3.074696996425587</v>
       </c>
       <c r="G75">
-        <v>-6.434029382815621</v>
+        <v>-7.089357604120149</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>0.02847245490190411</v>
       </c>
       <c r="E76">
-        <v>-23.97872608746815</v>
+        <v>-20.99721458838891</v>
       </c>
       <c r="F76">
-        <v>-2.819197011440913</v>
+        <v>-3.359020025190669</v>
       </c>
       <c r="G76">
-        <v>-6.401455122552301</v>
+        <v>-7.184644560206602</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>0.4210991368749927</v>
       </c>
       <c r="E77">
-        <v>-23.92466373565286</v>
+        <v>-21.39088918344676</v>
       </c>
       <c r="F77">
-        <v>-2.26703629359386</v>
+        <v>-3.63834468504726</v>
       </c>
       <c r="G77">
-        <v>-7.032566077029662</v>
+        <v>-6.475166885337793</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>0.808396776996177</v>
       </c>
       <c r="E78">
-        <v>-23.16417336317483</v>
+        <v>-23.88662447312875</v>
       </c>
       <c r="F78">
-        <v>-2.441532715360979</v>
+        <v>-3.404499880706571</v>
       </c>
       <c r="G78">
-        <v>-5.90851782555961</v>
+        <v>-6.184572737134746</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>1.180045764856262</v>
       </c>
       <c r="E79">
-        <v>-23.56050601348057</v>
+        <v>-22.37105536252895</v>
       </c>
       <c r="F79">
-        <v>-2.753493394153065</v>
+        <v>-3.419796513166666</v>
       </c>
       <c r="G79">
-        <v>-5.193716842469521</v>
+        <v>-5.904635648352625</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>1.530851444967376</v>
       </c>
       <c r="E80">
-        <v>-24.83881462072689</v>
+        <v>-24.43820416275658</v>
       </c>
       <c r="F80">
-        <v>-2.519416646939591</v>
+        <v>-4.157021135738351</v>
       </c>
       <c r="G80">
-        <v>-4.729019969718903</v>
+        <v>-6.334379872517419</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>1.852205647447413</v>
       </c>
       <c r="E81">
-        <v>-26.79382256197283</v>
+        <v>-23.44498859369179</v>
       </c>
       <c r="F81">
-        <v>-2.511662299681985</v>
+        <v>-3.561825902948461</v>
       </c>
       <c r="G81">
-        <v>-4.035420843453245</v>
+        <v>-5.706245166873926</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>2.135437485929823</v>
       </c>
       <c r="E82">
-        <v>-27.01797553038515</v>
+        <v>-25.78499922474933</v>
       </c>
       <c r="F82">
-        <v>-2.883612517417408</v>
+        <v>-3.538821311805316</v>
       </c>
       <c r="G82">
-        <v>-5.157678124133794</v>
+        <v>-5.413802611500372</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>2.375778376760446</v>
       </c>
       <c r="E83">
-        <v>-26.99358787348576</v>
+        <v>-27.05684958838555</v>
       </c>
       <c r="F83">
-        <v>-2.953367679672349</v>
+        <v>-3.713900075856603</v>
       </c>
       <c r="G83">
-        <v>-3.028869152306247</v>
+        <v>-6.009101982421432</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>2.566545201840497</v>
       </c>
       <c r="E84">
-        <v>-29.13485488301629</v>
+        <v>-26.49091224720779</v>
       </c>
       <c r="F84">
-        <v>-2.590094610481251</v>
+        <v>-3.802984363088467</v>
       </c>
       <c r="G84">
-        <v>-3.047016437959075</v>
+        <v>-5.660812989499373</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>2.701942021948653</v>
       </c>
       <c r="E85">
-        <v>-29.91969968670311</v>
+        <v>-28.42096354160283</v>
       </c>
       <c r="F85">
-        <v>-3.011811485042062</v>
+        <v>-3.805582123263647</v>
       </c>
       <c r="G85">
-        <v>-3.196575552605591</v>
+        <v>-5.216670508914589</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>2.778585396097258</v>
       </c>
       <c r="E86">
-        <v>-29.53442703815539</v>
+        <v>-30.1440312432024</v>
       </c>
       <c r="F86">
-        <v>-3.445709502261041</v>
+        <v>-4.067210370294231</v>
       </c>
       <c r="G86">
-        <v>-3.39829734418255</v>
+        <v>-4.638406246450543</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>2.792845450978036</v>
       </c>
       <c r="E87">
-        <v>-31.9652704774926</v>
+        <v>-30.99913176966002</v>
       </c>
       <c r="F87">
-        <v>-2.486359817363474</v>
+        <v>-3.147870002584478</v>
       </c>
       <c r="G87">
-        <v>-3.847948495854583</v>
+        <v>-5.427409812309254</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>2.742902154102085</v>
       </c>
       <c r="E88">
-        <v>-32.44874788442156</v>
+        <v>-32.10358279763771</v>
       </c>
       <c r="F88">
-        <v>-2.507467447154208</v>
+        <v>-3.037342596763746</v>
       </c>
       <c r="G88">
-        <v>-3.505249107102097</v>
+        <v>-6.012362802415733</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>2.627194315507352</v>
       </c>
       <c r="E89">
-        <v>-34.65881906936485</v>
+        <v>-33.48650249173382</v>
       </c>
       <c r="F89">
-        <v>-2.925535363305688</v>
+        <v>-3.615604343105608</v>
       </c>
       <c r="G89">
-        <v>-2.434708066026912</v>
+        <v>-6.003496713784312</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>2.445179958927345</v>
       </c>
       <c r="E90">
-        <v>-37.24867651069577</v>
+        <v>-34.0002048940792</v>
       </c>
       <c r="F90">
-        <v>-2.552756778167466</v>
+        <v>-3.430238912646357</v>
       </c>
       <c r="G90">
-        <v>-4.148975179443718</v>
+        <v>-5.979751991728136</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>2.199698937925288</v>
       </c>
       <c r="E91">
-        <v>-39.1767010379643</v>
+        <v>-36.86189416983148</v>
       </c>
       <c r="F91">
-        <v>-3.197272177752635</v>
+        <v>-3.393966360812572</v>
       </c>
       <c r="G91">
-        <v>-4.05656004240749</v>
+        <v>-6.232370249108849</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>1.890605080977751</v>
       </c>
       <c r="E92">
-        <v>-39.14047049897216</v>
+        <v>-38.73140825595582</v>
       </c>
       <c r="F92">
-        <v>-2.174447183880751</v>
+        <v>-2.710123390412094</v>
       </c>
       <c r="G92">
-        <v>-3.818846525897443</v>
+        <v>-6.490797413204788</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>1.520557720222726</v>
       </c>
       <c r="E93">
-        <v>-41.65818665959081</v>
+        <v>-40.05500347948808</v>
       </c>
       <c r="F93">
-        <v>-2.705128334973212</v>
+        <v>-2.369312331715307</v>
       </c>
       <c r="G93">
-        <v>-4.971263128094532</v>
+        <v>-6.416774971812954</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>1.097593406764488</v>
       </c>
       <c r="E94">
-        <v>-40.58219758882218</v>
+        <v>-40.42308390975667</v>
       </c>
       <c r="F94">
-        <v>-3.17217844401963</v>
+        <v>-2.393386345175466</v>
       </c>
       <c r="G94">
-        <v>-3.843692982171068</v>
+        <v>-7.505909735866047</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>0.6265806640966792</v>
       </c>
       <c r="E95">
-        <v>-44.60833933656193</v>
+        <v>-43.84162537691365</v>
       </c>
       <c r="F95">
-        <v>-2.249022616052582</v>
+        <v>-1.920666889624289</v>
       </c>
       <c r="G95">
-        <v>-5.342320424595689</v>
+        <v>-8.515818844557218</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>0.1107947025015807</v>
       </c>
       <c r="E96">
-        <v>-46.48752209865047</v>
+        <v>-45.23838980096107</v>
       </c>
       <c r="F96">
-        <v>-3.020342012556092</v>
+        <v>-0.9089817805852528</v>
       </c>
       <c r="G96">
-        <v>-5.199875588959958</v>
+        <v>-8.064619521342655</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-0.4310305665842841</v>
       </c>
       <c r="E97">
-        <v>-48.16944393565497</v>
+        <v>-47.7250233280247</v>
       </c>
       <c r="F97">
-        <v>-1.67176402263551</v>
+        <v>-1.061391442291528</v>
       </c>
       <c r="G97">
-        <v>-5.362942696120894</v>
+        <v>-8.483927294004474</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-1.004293354176892</v>
       </c>
       <c r="E98">
-        <v>-49.87338921401219</v>
+        <v>-48.81999465115346</v>
       </c>
       <c r="F98">
-        <v>-1.586426441166508</v>
+        <v>-0.5285615061562051</v>
       </c>
       <c r="G98">
-        <v>-6.024604583803463</v>
+        <v>-8.793480669428185</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-1.582978058679079</v>
       </c>
       <c r="E99">
-        <v>-53.63493090654995</v>
+        <v>-52.61139585651107</v>
       </c>
       <c r="F99">
-        <v>-2.193077166769712</v>
+        <v>0.06282820678522355</v>
       </c>
       <c r="G99">
-        <v>-6.138482652123233</v>
+        <v>-9.596087519978891</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-2.181436132377184</v>
       </c>
       <c r="E100">
-        <v>-53.64382085539074</v>
+        <v>-53.93971951113664</v>
       </c>
       <c r="F100">
-        <v>-1.376982855410084</v>
+        <v>0.4623655441360783</v>
       </c>
       <c r="G100">
-        <v>-7.47826717213534</v>
+        <v>-9.827614877180295</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-2.747426955851848</v>
       </c>
       <c r="E101">
-        <v>-56.94226391066764</v>
+        <v>-55.43180584575445</v>
       </c>
       <c r="F101">
-        <v>-1.128079160053902</v>
+        <v>0.9730954663321135</v>
       </c>
       <c r="G101">
-        <v>-7.59906371362156</v>
+        <v>-10.32792883301518</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-3.348328918390559</v>
       </c>
       <c r="E102">
-        <v>-58.45806508195022</v>
+        <v>-58.26770835154228</v>
       </c>
       <c r="F102">
-        <v>-0.8332665148671696</v>
+        <v>1.279950916820745</v>
       </c>
       <c r="G102">
-        <v>-7.081632410875045</v>
+        <v>-10.99520773768553</v>
       </c>
     </row>
   </sheetData>
